--- a/public/samples/S01_固定資産台帳_2027年3月期.xlsx
+++ b/public/samples/S01_固定資産台帳_2027年3月期.xlsx
@@ -735,7 +735,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="1">
-        <v>41730</v>
+        <v>42461</v>
       </c>
       <c r="E8" s="2">
         <v>20000000</v>
